--- a/template/8.5/净值.xlsx
+++ b/template/8.5/净值.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -3649,110 +3649,18 @@
           <t>2025/08/05</t>
         </is>
       </c>
-      <c r="B114" s="0" t="n">
+      <c r="B114" t="n">
         <v>0.99862</v>
       </c>
-      <c r="C114" s="0" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>-0.1422%</t>
         </is>
       </c>
-      <c r="D114" s="0" t="n">
+      <c r="D114" t="n">
         <v>0.99309</v>
       </c>
-      <c r="E114" s="0" t="inlineStr">
-        <is>
-          <t>-0.6954%</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B115" s="0" t="n">
-        <v>0.99862</v>
-      </c>
-      <c r="C115" s="0" t="inlineStr">
-        <is>
-          <t>-0.1422%</t>
-        </is>
-      </c>
-      <c r="D115" s="0" t="n">
-        <v>0.99309</v>
-      </c>
-      <c r="E115" s="0" t="inlineStr">
-        <is>
-          <t>-0.6954%</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B116" s="0" t="n">
-        <v>0.99862</v>
-      </c>
-      <c r="C116" s="0" t="inlineStr">
-        <is>
-          <t>-0.1422%</t>
-        </is>
-      </c>
-      <c r="D116" s="0" t="n">
-        <v>0.99309</v>
-      </c>
-      <c r="E116" s="0" t="inlineStr">
-        <is>
-          <t>-0.6954%</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B117" s="0" t="n">
-        <v>0.99862</v>
-      </c>
-      <c r="C117" s="0" t="inlineStr">
-        <is>
-          <t>-0.1422%</t>
-        </is>
-      </c>
-      <c r="D117" s="0" t="n">
-        <v>0.99309</v>
-      </c>
-      <c r="E117" s="0" t="inlineStr">
-        <is>
-          <t>-0.6954%</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>0.99862</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>-0.1422%</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>0.99309</v>
-      </c>
-      <c r="E118" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>-0.6954%</t>
         </is>
@@ -3770,7 +3678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E118"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -6386,110 +6294,18 @@
           <t>2025/08/05</t>
         </is>
       </c>
-      <c r="B114" s="0" t="n">
+      <c r="B114" t="n">
         <v>0.9975000000000001</v>
       </c>
-      <c r="C114" s="0" t="inlineStr">
+      <c r="C114" t="inlineStr">
         <is>
           <t>-0.2539%</t>
         </is>
       </c>
-      <c r="D114" s="0" t="n">
+      <c r="D114" t="n">
         <v>0.99197</v>
       </c>
-      <c r="E114" s="0" t="inlineStr">
-        <is>
-          <t>-0.807%</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B115" s="0" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="C115" s="0" t="inlineStr">
-        <is>
-          <t>-0.2539%</t>
-        </is>
-      </c>
-      <c r="D115" s="0" t="n">
-        <v>0.99197</v>
-      </c>
-      <c r="E115" s="0" t="inlineStr">
-        <is>
-          <t>-0.807%</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B116" s="0" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="C116" s="0" t="inlineStr">
-        <is>
-          <t>-0.2539%</t>
-        </is>
-      </c>
-      <c r="D116" s="0" t="n">
-        <v>0.99197</v>
-      </c>
-      <c r="E116" s="0" t="inlineStr">
-        <is>
-          <t>-0.807%</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B117" s="0" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="C117" s="0" t="inlineStr">
-        <is>
-          <t>-0.2539%</t>
-        </is>
-      </c>
-      <c r="D117" s="0" t="n">
-        <v>0.99197</v>
-      </c>
-      <c r="E117" s="0" t="inlineStr">
-        <is>
-          <t>-0.807%</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B118" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>-0.2539%</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>0.99197</v>
-      </c>
-      <c r="E118" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>-0.807%</t>
         </is>
@@ -6507,7 +6323,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -8734,110 +8550,18 @@
           <t>2025/08/05</t>
         </is>
       </c>
-      <c r="B97" s="0" t="n">
+      <c r="B97" t="n">
         <v>0.98632</v>
       </c>
-      <c r="C97" s="0" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>-3.6885%</t>
         </is>
       </c>
-      <c r="D97" s="0" t="n">
+      <c r="D97" t="n">
         <v>0.98561</v>
       </c>
-      <c r="E97" s="0" t="inlineStr">
-        <is>
-          <t>-3.7365%</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B98" s="0" t="n">
-        <v>0.98632</v>
-      </c>
-      <c r="C98" s="0" t="inlineStr">
-        <is>
-          <t>-3.6885%</t>
-        </is>
-      </c>
-      <c r="D98" s="0" t="n">
-        <v>0.98561</v>
-      </c>
-      <c r="E98" s="0" t="inlineStr">
-        <is>
-          <t>-3.7365%</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B99" s="0" t="n">
-        <v>0.98632</v>
-      </c>
-      <c r="C99" s="0" t="inlineStr">
-        <is>
-          <t>-3.6885%</t>
-        </is>
-      </c>
-      <c r="D99" s="0" t="n">
-        <v>0.98561</v>
-      </c>
-      <c r="E99" s="0" t="inlineStr">
-        <is>
-          <t>-3.7365%</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B100" s="0" t="n">
-        <v>0.98632</v>
-      </c>
-      <c r="C100" s="0" t="inlineStr">
-        <is>
-          <t>-3.6885%</t>
-        </is>
-      </c>
-      <c r="D100" s="0" t="n">
-        <v>0.98561</v>
-      </c>
-      <c r="E100" s="0" t="inlineStr">
-        <is>
-          <t>-3.7365%</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>0.98632</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>-3.6885%</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>0.98561</v>
-      </c>
-      <c r="E101" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>-3.7365%</t>
         </is>
@@ -8854,7 +8578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E101"/>
+  <dimension ref="A1:E97"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -11081,110 +10805,18 @@
           <t>2025/08/05</t>
         </is>
       </c>
-      <c r="B97" s="0" t="n">
+      <c r="B97" t="n">
         <v>1.00315</v>
       </c>
-      <c r="C97" s="0" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>-2.4484%</t>
         </is>
       </c>
-      <c r="D97" s="0" t="n">
+      <c r="D97" t="n">
         <v>1.00244</v>
       </c>
-      <c r="E97" s="0" t="inlineStr">
-        <is>
-          <t>-2.496%</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B98" s="0" t="n">
-        <v>1.00315</v>
-      </c>
-      <c r="C98" s="0" t="inlineStr">
-        <is>
-          <t>-2.4484%</t>
-        </is>
-      </c>
-      <c r="D98" s="0" t="n">
-        <v>1.00244</v>
-      </c>
-      <c r="E98" s="0" t="inlineStr">
-        <is>
-          <t>-2.496%</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B99" s="0" t="n">
-        <v>1.00315</v>
-      </c>
-      <c r="C99" s="0" t="inlineStr">
-        <is>
-          <t>-2.4484%</t>
-        </is>
-      </c>
-      <c r="D99" s="0" t="n">
-        <v>1.00244</v>
-      </c>
-      <c r="E99" s="0" t="inlineStr">
-        <is>
-          <t>-2.496%</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B100" s="0" t="n">
-        <v>1.00315</v>
-      </c>
-      <c r="C100" s="0" t="inlineStr">
-        <is>
-          <t>-2.4484%</t>
-        </is>
-      </c>
-      <c r="D100" s="0" t="n">
-        <v>1.00244</v>
-      </c>
-      <c r="E100" s="0" t="inlineStr">
-        <is>
-          <t>-2.496%</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B101" t="n">
-        <v>1.00315</v>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>-2.4484%</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>1.00244</v>
-      </c>
-      <c r="E101" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>-2.496%</t>
         </is>
@@ -11202,7 +10834,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -12187,110 +11819,18 @@
           <t>2025/08/05</t>
         </is>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" t="n">
         <v>0.98965</v>
       </c>
-      <c r="C43" s="0" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>-1.1139%</t>
         </is>
       </c>
-      <c r="D43" s="0" t="n">
+      <c r="D43" t="n">
         <v>0.98759</v>
       </c>
-      <c r="E43" s="0" t="inlineStr">
-        <is>
-          <t>-1.309%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B44" s="0" t="n">
-        <v>0.98965</v>
-      </c>
-      <c r="C44" s="0" t="inlineStr">
-        <is>
-          <t>-1.1139%</t>
-        </is>
-      </c>
-      <c r="D44" s="0" t="n">
-        <v>0.98759</v>
-      </c>
-      <c r="E44" s="0" t="inlineStr">
-        <is>
-          <t>-1.309%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B45" s="0" t="n">
-        <v>0.98965</v>
-      </c>
-      <c r="C45" s="0" t="inlineStr">
-        <is>
-          <t>-1.1139%</t>
-        </is>
-      </c>
-      <c r="D45" s="0" t="n">
-        <v>0.98759</v>
-      </c>
-      <c r="E45" s="0" t="inlineStr">
-        <is>
-          <t>-1.309%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B46" s="0" t="n">
-        <v>0.98965</v>
-      </c>
-      <c r="C46" s="0" t="inlineStr">
-        <is>
-          <t>-1.1139%</t>
-        </is>
-      </c>
-      <c r="D46" s="0" t="n">
-        <v>0.98759</v>
-      </c>
-      <c r="E46" s="0" t="inlineStr">
-        <is>
-          <t>-1.309%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0.98965</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>-1.1139%</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>0.98759</v>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>-1.309%</t>
         </is>
@@ -12307,7 +11847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E47"/>
+  <dimension ref="A1:E43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -13292,110 +12832,18 @@
           <t>2025/08/05</t>
         </is>
       </c>
-      <c r="B43" s="0" t="n">
+      <c r="B43" t="n">
         <v>0.98965</v>
       </c>
-      <c r="C43" s="0" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>-1.1139%</t>
         </is>
       </c>
-      <c r="D43" s="0" t="n">
+      <c r="D43" t="n">
         <v>0.98759</v>
       </c>
-      <c r="E43" s="0" t="inlineStr">
-        <is>
-          <t>-1.309%</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B44" s="0" t="n">
-        <v>0.98965</v>
-      </c>
-      <c r="C44" s="0" t="inlineStr">
-        <is>
-          <t>-1.1139%</t>
-        </is>
-      </c>
-      <c r="D44" s="0" t="n">
-        <v>0.98759</v>
-      </c>
-      <c r="E44" s="0" t="inlineStr">
-        <is>
-          <t>-1.309%</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B45" s="0" t="n">
-        <v>0.98965</v>
-      </c>
-      <c r="C45" s="0" t="inlineStr">
-        <is>
-          <t>-1.1139%</t>
-        </is>
-      </c>
-      <c r="D45" s="0" t="n">
-        <v>0.98759</v>
-      </c>
-      <c r="E45" s="0" t="inlineStr">
-        <is>
-          <t>-1.309%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B46" s="0" t="n">
-        <v>0.98965</v>
-      </c>
-      <c r="C46" s="0" t="inlineStr">
-        <is>
-          <t>-1.1139%</t>
-        </is>
-      </c>
-      <c r="D46" s="0" t="n">
-        <v>0.98759</v>
-      </c>
-      <c r="E46" s="0" t="inlineStr">
-        <is>
-          <t>-1.309%</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0.98965</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>-1.1139%</t>
-        </is>
-      </c>
-      <c r="D47" t="n">
-        <v>0.98759</v>
-      </c>
-      <c r="E47" t="inlineStr">
+      <c r="E43" t="inlineStr">
         <is>
           <t>-1.309%</t>
         </is>

--- a/template/8.5/净值.xlsx
+++ b/template/8.5/净值.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -3626,43 +3626,20 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B113" s="0" t="n">
+      <c r="B113" t="n">
         <v>0.99823</v>
       </c>
-      <c r="C113" s="0" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>-0.1814%</t>
         </is>
       </c>
-      <c r="D113" s="0" t="n">
+      <c r="D113" t="n">
         <v>0.99211</v>
       </c>
-      <c r="E113" s="0" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>-0.7927%</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>0.99862</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>-0.1422%</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>0.99309</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>-0.6954%</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E114"/>
+  <dimension ref="A1:E113"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -6271,43 +6248,20 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B113" s="0" t="n">
+      <c r="B113" t="n">
         <v>0.99805</v>
       </c>
-      <c r="C113" s="0" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>-0.199%</t>
         </is>
       </c>
-      <c r="D113" s="0" t="n">
+      <c r="D113" t="n">
         <v>0.99194</v>
       </c>
-      <c r="E113" s="0" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>-0.8103%</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B114" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>-0.2539%</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>0.99197</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>-0.807%</t>
         </is>
       </c>
     </row>
@@ -6323,7 +6277,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -8527,43 +8481,20 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B96" s="0" t="n">
+      <c r="B96" t="n">
         <v>0.98612</v>
       </c>
-      <c r="C96" s="0" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>-3.7078%</t>
         </is>
       </c>
-      <c r="D96" s="0" t="n">
+      <c r="D96" t="n">
         <v>0.9825</v>
       </c>
-      <c r="E96" s="0" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>-4.0398%</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>0.98632</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>-3.6885%</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>0.98561</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>-3.7365%</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E97"/>
+  <dimension ref="A1:E96"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -10782,43 +10713,20 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B96" s="0" t="n">
+      <c r="B96" t="n">
         <v>0.98622</v>
       </c>
-      <c r="C96" s="0" t="inlineStr">
+      <c r="C96" t="inlineStr">
         <is>
           <t>-4.0952%</t>
         </is>
       </c>
-      <c r="D96" s="0" t="n">
+      <c r="D96" t="n">
         <v>0.9826</v>
       </c>
-      <c r="E96" s="0" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>-4.4259%</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B97" t="n">
-        <v>1.00315</v>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>-2.4484%</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>1.00244</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>-2.496%</t>
         </is>
       </c>
     </row>
@@ -10834,7 +10742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -11796,43 +11704,20 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42" t="n">
         <v>0.9895699999999999</v>
       </c>
-      <c r="C42" s="0" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>-1.1218%</t>
         </is>
       </c>
-      <c r="D42" s="0" t="n">
+      <c r="D42" t="n">
         <v>0.9882300000000001</v>
       </c>
-      <c r="E42" s="0" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>-1.2444%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0.98965</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>-1.1139%</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>0.98759</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-1.309%</t>
         </is>
       </c>
     </row>
@@ -11847,7 +11732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -12809,43 +12694,20 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B42" s="0" t="n">
+      <c r="B42" t="n">
         <v>0.9895699999999999</v>
       </c>
-      <c r="C42" s="0" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>-1.1219%</t>
         </is>
       </c>
-      <c r="D42" s="0" t="n">
+      <c r="D42" t="n">
         <v>0.9882300000000001</v>
       </c>
-      <c r="E42" s="0" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>-1.2444%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0.98965</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>-1.1139%</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>0.98759</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>-1.309%</t>
         </is>
       </c>
     </row>

--- a/template/8.5/净值.xlsx
+++ b/template/8.5/净值.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -3626,20 +3626,135 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" s="0" t="n">
         <v>0.99823</v>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="0" t="inlineStr">
         <is>
           <t>-0.1814%</t>
         </is>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="0" t="n">
         <v>0.99211</v>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E113" s="0" t="inlineStr">
         <is>
           <t>-0.7927%</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B114" s="0" t="n">
+        <v>0.99862</v>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t>-0.1422%</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="n">
+        <v>0.99309</v>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t>-0.6954%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B115" s="0" t="n">
+        <v>0.99862</v>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>-0.1422%</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="n">
+        <v>0.99309</v>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t>-0.6954%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B116" s="0" t="n">
+        <v>0.99862</v>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>-0.1422%</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="n">
+        <v>0.99309</v>
+      </c>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t>-0.6954%</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B117" s="0" t="n">
+        <v>0.99862</v>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t>-0.1422%</t>
+        </is>
+      </c>
+      <c r="D117" s="0" t="n">
+        <v>0.99309</v>
+      </c>
+      <c r="E117" s="0" t="inlineStr">
+        <is>
+          <t>-0.6954%</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0.99862</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>-0.1422%</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0.99309</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-0.6954%</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3770,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E118"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -6248,20 +6363,135 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" s="0" t="n">
         <v>0.99805</v>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="0" t="inlineStr">
         <is>
           <t>-0.199%</t>
         </is>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="0" t="n">
         <v>0.99194</v>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E113" s="0" t="inlineStr">
         <is>
           <t>-0.8103%</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B114" s="0" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t>-0.2539%</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="n">
+        <v>0.99197</v>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t>-0.807%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B115" s="0" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>-0.2539%</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="n">
+        <v>0.99197</v>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t>-0.807%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B116" s="0" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>-0.2539%</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="n">
+        <v>0.99197</v>
+      </c>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t>-0.807%</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B117" s="0" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="C117" s="0" t="inlineStr">
+        <is>
+          <t>-0.2539%</t>
+        </is>
+      </c>
+      <c r="D117" s="0" t="n">
+        <v>0.99197</v>
+      </c>
+      <c r="E117" s="0" t="inlineStr">
+        <is>
+          <t>-0.807%</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>-0.2539%</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0.99197</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>-0.807%</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -8481,20 +8711,135 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" s="0" t="n">
         <v>0.98612</v>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="0" t="inlineStr">
         <is>
           <t>-3.7078%</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="0" t="n">
         <v>0.9825</v>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" s="0" t="inlineStr">
         <is>
           <t>-4.0398%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="n">
+        <v>0.98632</v>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>-3.6885%</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="n">
+        <v>0.98561</v>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
+        <is>
+          <t>-3.7365%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="n">
+        <v>0.98632</v>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>-3.6885%</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="n">
+        <v>0.98561</v>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t>-3.7365%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="n">
+        <v>0.98632</v>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>-3.6885%</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="n">
+        <v>0.98561</v>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t>-3.7365%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B100" s="0" t="n">
+        <v>0.98632</v>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>-3.6885%</t>
+        </is>
+      </c>
+      <c r="D100" s="0" t="n">
+        <v>0.98561</v>
+      </c>
+      <c r="E100" s="0" t="inlineStr">
+        <is>
+          <t>-3.7365%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0.98632</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>-3.6885%</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>0.98561</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-3.7365%</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -10713,20 +11058,135 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" s="0" t="n">
         <v>0.98622</v>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="0" t="inlineStr">
         <is>
           <t>-4.0952%</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="0" t="n">
         <v>0.9826</v>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" s="0" t="inlineStr">
         <is>
           <t>-4.4259%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B100" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C100" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D100" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E100" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
         </is>
       </c>
     </row>
@@ -10742,7 +11202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -11704,20 +12164,135 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="0" t="n">
         <v>0.9895699999999999</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>-1.1218%</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="0" t="n">
         <v>0.9882300000000001</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>-1.2444%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>0.98965</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>-1.1139%</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>0.98759</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>-1.309%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>0.98965</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>-1.1139%</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>0.98759</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>-1.309%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>0.98965</v>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>-1.1139%</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>0.98759</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>-1.309%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>0.98965</v>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>-1.1139%</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>0.98759</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>-1.309%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.98965</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>-1.1139%</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.98759</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-1.309%</t>
         </is>
       </c>
     </row>
@@ -11732,7 +12307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E47"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -12694,20 +13269,135 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="0" t="n">
         <v>0.9895699999999999</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>-1.1219%</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="0" t="n">
         <v>0.9882300000000001</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>-1.2444%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>0.98965</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>-1.1139%</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>0.98759</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>-1.309%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>0.98965</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>-1.1139%</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>0.98759</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>-1.309%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>0.98965</v>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>-1.1139%</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>0.98759</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>-1.309%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B46" s="0" t="n">
+        <v>0.98965</v>
+      </c>
+      <c r="C46" s="0" t="inlineStr">
+        <is>
+          <t>-1.1139%</t>
+        </is>
+      </c>
+      <c r="D46" s="0" t="n">
+        <v>0.98759</v>
+      </c>
+      <c r="E46" s="0" t="inlineStr">
+        <is>
+          <t>-1.309%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.98965</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>-1.1139%</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.98759</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-1.309%</t>
         </is>
       </c>
     </row>

--- a/template/8.5/净值.xlsx
+++ b/template/8.5/净值.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -3626,20 +3626,112 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" s="0" t="n">
         <v>0.99823</v>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="0" t="inlineStr">
         <is>
           <t>-0.1814%</t>
         </is>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="0" t="n">
         <v>0.99211</v>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E113" s="0" t="inlineStr">
         <is>
           <t>-0.7927%</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B114" s="0" t="n">
+        <v>0.99862</v>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t>-0.1422%</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="n">
+        <v>0.99309</v>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t>-0.6954%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B115" s="0" t="n">
+        <v>0.99862</v>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>-0.1422%</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="n">
+        <v>0.99309</v>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t>-0.6954%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B116" s="0" t="n">
+        <v>0.99862</v>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>-0.1422%</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="n">
+        <v>0.99309</v>
+      </c>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t>-0.6954%</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0.99862</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>-0.1422%</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0.99309</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-0.6954%</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3747,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E113"/>
+  <dimension ref="A1:E117"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -6248,20 +6340,112 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B113" t="n">
+      <c r="B113" s="0" t="n">
         <v>0.99805</v>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C113" s="0" t="inlineStr">
         <is>
           <t>-0.199%</t>
         </is>
       </c>
-      <c r="D113" t="n">
+      <c r="D113" s="0" t="n">
         <v>0.99194</v>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E113" s="0" t="inlineStr">
         <is>
           <t>-0.8103%</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B114" s="0" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="C114" s="0" t="inlineStr">
+        <is>
+          <t>-0.2539%</t>
+        </is>
+      </c>
+      <c r="D114" s="0" t="n">
+        <v>0.99197</v>
+      </c>
+      <c r="E114" s="0" t="inlineStr">
+        <is>
+          <t>-0.807%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B115" s="0" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="C115" s="0" t="inlineStr">
+        <is>
+          <t>-0.2539%</t>
+        </is>
+      </c>
+      <c r="D115" s="0" t="n">
+        <v>0.99197</v>
+      </c>
+      <c r="E115" s="0" t="inlineStr">
+        <is>
+          <t>-0.807%</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B116" s="0" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="C116" s="0" t="inlineStr">
+        <is>
+          <t>-0.2539%</t>
+        </is>
+      </c>
+      <c r="D116" s="0" t="n">
+        <v>0.99197</v>
+      </c>
+      <c r="E116" s="0" t="inlineStr">
+        <is>
+          <t>-0.807%</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0.9975000000000001</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>-0.2539%</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>0.99197</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>-0.807%</t>
         </is>
       </c>
     </row>
@@ -6277,7 +6461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -8481,20 +8665,112 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" s="0" t="n">
         <v>0.98612</v>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="0" t="inlineStr">
         <is>
           <t>-3.7078%</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="0" t="n">
         <v>0.9825</v>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" s="0" t="inlineStr">
         <is>
           <t>-4.0398%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="n">
+        <v>0.98632</v>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>-3.6885%</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="n">
+        <v>0.98561</v>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
+        <is>
+          <t>-3.7365%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="n">
+        <v>0.98632</v>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>-3.6885%</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="n">
+        <v>0.98561</v>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t>-3.7365%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="n">
+        <v>0.98632</v>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>-3.6885%</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="n">
+        <v>0.98561</v>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t>-3.7365%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.98632</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>-3.6885%</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>0.98561</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-3.7365%</t>
         </is>
       </c>
     </row>
@@ -8509,7 +8785,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:E100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -10713,20 +10989,112 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B96" t="n">
+      <c r="B96" s="0" t="n">
         <v>0.98622</v>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C96" s="0" t="inlineStr">
         <is>
           <t>-4.0952%</t>
         </is>
       </c>
-      <c r="D96" t="n">
+      <c r="D96" s="0" t="n">
         <v>0.9826</v>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E96" s="0" t="inlineStr">
         <is>
           <t>-4.4259%</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B97" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C97" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D97" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B98" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C98" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D98" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B99" s="0" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1.00315</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>-2.4484%</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>1.00244</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>-2.496%</t>
         </is>
       </c>
     </row>
@@ -10742,7 +11110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -11704,20 +12072,112 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="0" t="n">
         <v>0.9895699999999999</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>-1.1218%</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="0" t="n">
         <v>0.9882300000000001</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>-1.2444%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>0.98965</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>-1.1139%</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>0.98759</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>-1.309%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>0.98965</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>-1.1139%</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>0.98759</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>-1.309%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>0.98965</v>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>-1.1139%</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>0.98759</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>-1.309%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.98965</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>-1.1139%</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.98759</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>-1.309%</t>
         </is>
       </c>
     </row>
@@ -11732,7 +12192,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E46"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -12694,20 +13154,112 @@
           <t>2025/08/04</t>
         </is>
       </c>
-      <c r="B42" t="n">
+      <c r="B42" s="0" t="n">
         <v>0.9895699999999999</v>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>-1.1219%</t>
         </is>
       </c>
-      <c r="D42" t="n">
+      <c r="D42" s="0" t="n">
         <v>0.9882300000000001</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E42" s="0" t="inlineStr">
         <is>
           <t>-1.2444%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B43" s="0" t="n">
+        <v>1.17007</v>
+      </c>
+      <c r="C43" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="D43" s="0" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="E43" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B44" s="0" t="n">
+        <v>1.17007</v>
+      </c>
+      <c r="C44" s="0" t="inlineStr">
+        <is>
+          <t>-0.0003%</t>
+        </is>
+      </c>
+      <c r="D44" s="0" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="E44" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B45" s="0" t="n">
+        <v>1.17007</v>
+      </c>
+      <c r="C45" s="0" t="inlineStr">
+        <is>
+          <t>-0.0003%</t>
+        </is>
+      </c>
+      <c r="D45" s="0" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="E45" s="0" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>2025/08/05</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1.17007</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>-0.0003%</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>1.168</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
     </row>

--- a/template/8.5/净值.xlsx
+++ b/template/8.5/净值.xlsx
@@ -1033,7 +1033,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -3695,41 +3695,18 @@
           <t>2025/08/05</t>
         </is>
       </c>
-      <c r="B116" s="0" t="n">
+      <c r="B116" t="n">
         <v>0.99862</v>
       </c>
-      <c r="C116" s="0" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>-0.1422%</t>
         </is>
       </c>
-      <c r="D116" s="0" t="n">
+      <c r="D116" t="n">
         <v>0.99309</v>
       </c>
-      <c r="E116" s="0" t="inlineStr">
-        <is>
-          <t>-0.6954%</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>0.99862</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>-0.1422%</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>0.99309</v>
-      </c>
-      <c r="E117" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>-0.6954%</t>
         </is>
@@ -3747,7 +3724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E117"/>
+  <dimension ref="A1:E116"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -6409,41 +6386,18 @@
           <t>2025/08/05</t>
         </is>
       </c>
-      <c r="B116" s="0" t="n">
+      <c r="B116" t="n">
         <v>0.9975000000000001</v>
       </c>
-      <c r="C116" s="0" t="inlineStr">
+      <c r="C116" t="inlineStr">
         <is>
           <t>-0.2539%</t>
         </is>
       </c>
-      <c r="D116" s="0" t="n">
+      <c r="D116" t="n">
         <v>0.99197</v>
       </c>
-      <c r="E116" s="0" t="inlineStr">
-        <is>
-          <t>-0.807%</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B117" t="n">
-        <v>0.9975000000000001</v>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>-0.2539%</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>0.99197</v>
-      </c>
-      <c r="E117" t="inlineStr">
+      <c r="E116" t="inlineStr">
         <is>
           <t>-0.807%</t>
         </is>
@@ -6461,7 +6415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -8734,41 +8688,18 @@
           <t>2025/08/05</t>
         </is>
       </c>
-      <c r="B99" s="0" t="n">
+      <c r="B99" t="n">
         <v>0.98632</v>
       </c>
-      <c r="C99" s="0" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>-3.6885%</t>
         </is>
       </c>
-      <c r="D99" s="0" t="n">
+      <c r="D99" t="n">
         <v>0.98561</v>
       </c>
-      <c r="E99" s="0" t="inlineStr">
-        <is>
-          <t>-3.7365%</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>0.98632</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>-3.6885%</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>0.98561</v>
-      </c>
-      <c r="E100" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>-3.7365%</t>
         </is>
@@ -8785,7 +8716,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -11058,41 +10989,18 @@
           <t>2025/08/05</t>
         </is>
       </c>
-      <c r="B99" s="0" t="n">
+      <c r="B99" t="n">
         <v>1.00315</v>
       </c>
-      <c r="C99" s="0" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>-2.4484%</t>
         </is>
       </c>
-      <c r="D99" s="0" t="n">
+      <c r="D99" t="n">
         <v>1.00244</v>
       </c>
-      <c r="E99" s="0" t="inlineStr">
-        <is>
-          <t>-2.496%</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B100" t="n">
-        <v>1.00315</v>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>-2.4484%</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>1.00244</v>
-      </c>
-      <c r="E100" t="inlineStr">
+      <c r="E99" t="inlineStr">
         <is>
           <t>-2.496%</t>
         </is>
@@ -11110,7 +11018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -12141,41 +12049,18 @@
           <t>2025/08/05</t>
         </is>
       </c>
-      <c r="B45" s="0" t="n">
+      <c r="B45" t="n">
         <v>0.98965</v>
       </c>
-      <c r="C45" s="0" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>-1.1139%</t>
         </is>
       </c>
-      <c r="D45" s="0" t="n">
+      <c r="D45" t="n">
         <v>0.98759</v>
       </c>
-      <c r="E45" s="0" t="inlineStr">
-        <is>
-          <t>-1.309%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0.98965</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>-1.1139%</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>0.98759</v>
-      </c>
-      <c r="E46" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>-1.309%</t>
         </is>
@@ -12192,7 +12077,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E46"/>
+  <dimension ref="A1:E45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.4"/>
   <cols>
     <col width="11.6296296296296" customWidth="1" style="1" min="1" max="1"/>
@@ -13223,41 +13108,18 @@
           <t>2025/08/05</t>
         </is>
       </c>
-      <c r="B45" s="0" t="n">
+      <c r="B45" t="n">
         <v>1.17007</v>
       </c>
-      <c r="C45" s="0" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>-0.0003%</t>
         </is>
       </c>
-      <c r="D45" s="0" t="n">
+      <c r="D45" t="n">
         <v>1.168</v>
       </c>
-      <c r="E45" s="0" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
-        <is>
-          <t>2025/08/05</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>1.17007</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>-0.0003%</t>
-        </is>
-      </c>
-      <c r="D46" t="n">
-        <v>1.168</v>
-      </c>
-      <c r="E46" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>0%</t>
         </is>

--- a/template/8.5/净值.xlsx
+++ b/template/8.5/净值.xlsx
@@ -12035,11 +12035,11 @@
         </is>
       </c>
       <c r="D44" s="0" t="n">
-        <v>0.98759</v>
+        <v>-0.79013</v>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
-          <t>-1.309%</t>
+          <t>-178.9585%</t>
         </is>
       </c>
     </row>
@@ -12058,11 +12058,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>0.98759</v>
+        <v>-0.82143</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-1.309%</t>
+          <t>-182.0864%</t>
         </is>
       </c>
     </row>
@@ -13094,11 +13094,11 @@
         </is>
       </c>
       <c r="D44" s="0" t="n">
-        <v>1.168</v>
+        <v>-0.60971</v>
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>-152.2013%</t>
         </is>
       </c>
     </row>
@@ -13117,11 +13117,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1.168</v>
+        <v>-0.64101</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-154.8811%</t>
         </is>
       </c>
     </row>
